--- a/dokumen/Notulen Distribusi 14 Feb 2026.xlsx
+++ b/dokumen/Notulen Distribusi 14 Feb 2026.xlsx
@@ -444,7 +444,7 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="0" t="s">

--- a/dokumen/Notulen Distribusi 14 Feb 2026.xlsx
+++ b/dokumen/Notulen Distribusi 14 Feb 2026.xlsx
@@ -434,7 +434,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="41.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="64.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="50.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16.46"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -447,13 +447,13 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
